--- a/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_regression_results.xlsx
+++ b/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_regression_results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="261" uniqueCount="61">
   <si>
     <t>Phase 1 final baseline association models</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>model_note</t>
+  </si>
+  <si>
+    <t>df_residual</t>
   </si>
   <si>
     <t>idx_legal_classif_knowledge</t>
@@ -278,7 +281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -318,6 +321,9 @@
       <c r="L1" t="s">
         <v>32</v>
       </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -327,34 +333,37 @@
         <v>16</v>
       </c>
       <c r="C2" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="E2" s="1">
         <v>0.80842424793676892</v>
       </c>
       <c r="F2" s="1">
-        <v>0.13194006681442261</v>
+        <v>0.13013805449008942</v>
       </c>
       <c r="G2" s="1">
-        <v>0.13352385248784779</v>
+        <v>0.13075901602885559</v>
       </c>
       <c r="H2" s="1">
-        <v>0.023501584578491601</v>
+        <v>0.023335991400102701</v>
       </c>
       <c r="I2" s="1">
-        <v>0.086944475769996643</v>
+        <v>0.084517188370227814</v>
       </c>
       <c r="J2" s="1">
-        <v>0.18010322749614716</v>
+        <v>0.17700083553791046</v>
       </c>
       <c r="K2" s="1">
-        <v>1.12443364887e-07</v>
+        <v>1.5489128481199999e-07</v>
       </c>
       <c r="L2" t="s">
         <v>2</v>
+      </c>
+      <c r="M2" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="3">
@@ -365,34 +374,37 @@
         <v>17</v>
       </c>
       <c r="C3" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D3" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="E3" s="1">
         <v>0.74123304946856061</v>
       </c>
       <c r="F3" s="1">
-        <v>0.072526402771472931</v>
+        <v>0.072095766663551331</v>
       </c>
       <c r="G3" s="1">
-        <v>0.072686603949093695</v>
+        <v>0.072390912772540506</v>
       </c>
       <c r="H3" s="1">
-        <v>0.032381982855789103</v>
+        <v>0.032435450336743603</v>
       </c>
       <c r="I3" s="1">
-        <v>0.0085065662860870361</v>
+        <v>0.0081179030239582062</v>
       </c>
       <c r="J3" s="1">
-        <v>0.13686664402484894</v>
+        <v>0.13666392862796784</v>
       </c>
       <c r="K3" s="1">
-        <v>0.026809045293572899</v>
+        <v>0.027633536797177099</v>
       </c>
       <c r="L3" t="s">
         <v>2</v>
+      </c>
+      <c r="M3" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -403,34 +415,37 @@
         <v>18</v>
       </c>
       <c r="C4" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D4" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="E4" s="1">
         <v>0.6348355656320398</v>
       </c>
       <c r="F4" s="1">
-        <v>0.023997446522116661</v>
+        <v>0.023088051006197929</v>
       </c>
       <c r="G4" s="1">
-        <v>0.025643211987156099</v>
+        <v>0.023925287751462999</v>
       </c>
       <c r="H4" s="1">
-        <v>0.024697826990098402</v>
+        <v>0.024653485998332999</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.023307077586650848</v>
+        <v>-0.024927239865064621</v>
       </c>
       <c r="J4" s="1">
-        <v>0.074593499302864075</v>
+        <v>0.072777815163135529</v>
       </c>
       <c r="K4" s="1">
-        <v>0.30143838244592208</v>
+        <v>0.33392586668415231</v>
       </c>
       <c r="L4" t="s">
         <v>2</v>
+      </c>
+      <c r="M4" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -441,34 +456,37 @@
         <v>19</v>
       </c>
       <c r="C5" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="E5" s="1">
         <v>0.71757883917201648</v>
       </c>
       <c r="F5" s="1">
-        <v>0.076576575636863708</v>
+        <v>0.074861109256744385</v>
       </c>
       <c r="G5" s="1">
-        <v>0.077763251642035305</v>
+        <v>0.075351792348510097</v>
       </c>
       <c r="H5" s="1">
-        <v>0.019689713480136501</v>
+        <v>0.019670301982851499</v>
       </c>
       <c r="I5" s="1">
-        <v>0.038738880306482315</v>
+        <v>0.036373775452375412</v>
       </c>
       <c r="J5" s="1">
-        <v>0.1167876273393631</v>
+        <v>0.11432980746030807</v>
       </c>
       <c r="K5" s="1">
-        <v>0.000139252480855</v>
+        <v>0.0002120617825066</v>
       </c>
       <c r="L5" t="s">
         <v>2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -479,34 +497,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D6" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="E6" s="1">
         <v>0.71448863636363635</v>
       </c>
       <c r="F6" s="1">
-        <v>0.19144478440284729</v>
+        <v>0.18992422521114349</v>
       </c>
       <c r="G6" s="1">
-        <v>0.19408548999843289</v>
+        <v>0.19133539962063531</v>
       </c>
       <c r="H6" s="1">
-        <v>0.048675094284900897</v>
+        <v>0.048178752283829701</v>
       </c>
       <c r="I6" s="1">
-        <v>0.097613036632537842</v>
+        <v>0.095865987241268158</v>
       </c>
       <c r="J6" s="1">
-        <v>0.29055795073509216</v>
+        <v>0.28680482506752014</v>
       </c>
       <c r="K6" s="1">
-        <v>0.0001211881374594</v>
+        <v>0.0001272769286991</v>
       </c>
       <c r="L6" t="s">
         <v>2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -517,34 +538,37 @@
         <v>21</v>
       </c>
       <c r="C7" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D7" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="E7" s="1">
         <v>0.69829996065659961</v>
       </c>
       <c r="F7" s="1">
-        <v>0.083191156387329102</v>
+        <v>0.083090454339981079</v>
       </c>
       <c r="G7" s="1">
-        <v>0.086382323565427896</v>
+        <v>0.085053223485317797</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0374182898066431</v>
+        <v>0.037207968855664603</v>
       </c>
       <c r="I7" s="1">
-        <v>0.012220489792525768</v>
+        <v>0.011323149316012859</v>
       </c>
       <c r="J7" s="1">
-        <v>0.16054415702819824</v>
+        <v>0.15878330171108246</v>
       </c>
       <c r="K7" s="1">
-        <v>0.022854454520505899</v>
+        <v>0.0241592955839613</v>
       </c>
       <c r="L7" t="s">
         <v>2</v>
+      </c>
+      <c r="M7" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -555,34 +579,37 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D8" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="E8" s="1">
         <v>0.75931188193234533</v>
       </c>
       <c r="F8" s="1">
-        <v>0.061280738562345505</v>
+        <v>0.059715099632740021</v>
       </c>
       <c r="G8" s="1">
-        <v>0.050959189019124398</v>
+        <v>0.050797553231641999</v>
       </c>
       <c r="H8" s="1">
-        <v>0.050795663262046799</v>
+        <v>0.0507967899631682</v>
       </c>
       <c r="I8" s="1">
-        <v>-0.04971616342663765</v>
+        <v>-0.049859676510095596</v>
       </c>
       <c r="J8" s="1">
-        <v>0.15163454413414001</v>
+        <v>0.15145477652549744</v>
       </c>
       <c r="K8" s="1">
-        <v>0.31797699314107508</v>
+        <v>0.31947826824520409</v>
       </c>
       <c r="L8" t="s">
         <v>2</v>
+      </c>
+      <c r="M8" s="1">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -599,19 +626,19 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s">
         <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
         <v>28</v>
@@ -620,7 +647,7 @@
         <v>31</v>
       </c>
       <c r="I1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s">
         <v>32</v>
@@ -628,31 +655,31 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F2" s="1">
-        <v>0.060060767726405354</v>
+        <v>0.054786490305894747</v>
       </c>
       <c r="G2" s="1">
-        <v>0.037960745394229889</v>
+        <v>0.039074067026376724</v>
       </c>
       <c r="H2" s="1">
-        <v>0.11664477735757828</v>
+        <v>0.16380143165588379</v>
       </c>
       <c r="I2" s="1">
-        <v>0.12161314487457275</v>
+        <v>0.10531265288591385</v>
       </c>
       <c r="J2" t="s">
         <v>2</v>
@@ -660,31 +687,31 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.059411821088509821</v>
+        <v>-0.07230805971572124</v>
       </c>
       <c r="G3" s="1">
-        <v>0.053852006793022156</v>
+        <v>0.052658367902040482</v>
       </c>
       <c r="H3" s="1">
-        <v>0.27246814966201782</v>
+        <v>0.17260214686393738</v>
       </c>
       <c r="I3" s="1">
-        <v>0.12161314487457275</v>
+        <v>0.10531265288591385</v>
       </c>
       <c r="J3" t="s">
         <v>2</v>
@@ -692,31 +719,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.0013909456014202931</v>
+        <v>-0.001787409945209813</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0011272579431533813</v>
+        <v>0.0011465441202744842</v>
       </c>
       <c r="H4" s="1">
-        <v>0.2200140655040741</v>
+        <v>0.12198793143033981</v>
       </c>
       <c r="I4" s="1">
-        <v>0.12161314487457275</v>
+        <v>0.10531265288591385</v>
       </c>
       <c r="J4" t="s">
         <v>2</v>
@@ -724,31 +751,31 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.037125811046438598</v>
+        <v>-0.032357636346294856</v>
       </c>
       <c r="G5" s="1">
-        <v>0.029908062890172005</v>
+        <v>0.030845440924167633</v>
       </c>
       <c r="H5" s="1">
-        <v>0.2172759622335434</v>
+        <v>0.29655253887176514</v>
       </c>
       <c r="I5" s="1">
-        <v>0.12161314487457275</v>
+        <v>0.10531265288591385</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
@@ -756,31 +783,31 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F6" s="1">
-        <v>0.030493351747107371</v>
+        <v>0.029616434557541493</v>
       </c>
       <c r="G6" s="1">
-        <v>0.041299395263195038</v>
+        <v>0.042422045022249222</v>
       </c>
       <c r="H6" s="1">
-        <v>0.46196556091308594</v>
+        <v>0.48661971092224121</v>
       </c>
       <c r="I6" s="1">
-        <v>0.12161314487457275</v>
+        <v>0.10531265288591385</v>
       </c>
       <c r="J6" t="s">
         <v>2</v>
@@ -788,31 +815,31 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F7" s="1">
-        <v>0.056436126281735229</v>
+        <v>0.055850977870511388</v>
       </c>
       <c r="G7" s="1">
-        <v>0.033563479781150818</v>
+        <v>0.033267084509134293</v>
       </c>
       <c r="H7" s="1">
-        <v>0.09567154198884964</v>
+        <v>0.096123769879341125</v>
       </c>
       <c r="I7" s="1">
-        <v>0.12161314487457275</v>
+        <v>0.10531265288591385</v>
       </c>
       <c r="J7" t="s">
         <v>2</v>
@@ -820,31 +847,31 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F8" s="1">
-        <v>0.042023266694888845</v>
+        <v>0.040511193127084677</v>
       </c>
       <c r="G8" s="1">
-        <v>0.052259895950555801</v>
+        <v>0.052178643643856049</v>
       </c>
       <c r="H8" s="1">
-        <v>0.42316153645515442</v>
+        <v>0.43924528360366821</v>
       </c>
       <c r="I8" s="1">
-        <v>0.12451978772878647</v>
+        <v>0.1244753897190094</v>
       </c>
       <c r="J8" t="s">
         <v>2</v>
@@ -852,31 +879,31 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.14172716312434572</v>
+        <v>-0.13976691293908306</v>
       </c>
       <c r="G9" s="1">
-        <v>0.1016165167093277</v>
+        <v>0.098307818174362183</v>
       </c>
       <c r="H9" s="1">
-        <v>0.16607049107551575</v>
+        <v>0.15804104506969452</v>
       </c>
       <c r="I9" s="1">
-        <v>0.12451978772878647</v>
+        <v>0.1244753897190094</v>
       </c>
       <c r="J9" t="s">
         <v>2</v>
@@ -884,31 +911,31 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10" s="1">
-        <v>0.00067801038537156479</v>
+        <v>0.00057534178143837955</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0017883563414216042</v>
+        <v>0.001781858503818512</v>
       </c>
       <c r="H10" s="1">
-        <v>0.70536810159683228</v>
+        <v>0.74741566181182861</v>
       </c>
       <c r="I10" s="1">
-        <v>0.12451978772878647</v>
+        <v>0.1244753897190094</v>
       </c>
       <c r="J10" t="s">
         <v>2</v>
@@ -916,31 +943,31 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F11" s="1">
-        <v>0.033131340182770572</v>
+        <v>0.034897996396810564</v>
       </c>
       <c r="G11" s="1">
-        <v>0.041970368474721909</v>
+        <v>0.04239330068230629</v>
       </c>
       <c r="H11" s="1">
-        <v>0.43167522549629211</v>
+        <v>0.41224470734596252</v>
       </c>
       <c r="I11" s="1">
-        <v>0.12451978772878647</v>
+        <v>0.1244753897190094</v>
       </c>
       <c r="J11" t="s">
         <v>2</v>
@@ -948,31 +975,31 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" s="1">
-        <v>0.087456473173438354</v>
+        <v>0.087913888872063806</v>
       </c>
       <c r="G12" s="1">
-        <v>0.065950267016887665</v>
+        <v>0.065810516476631165</v>
       </c>
       <c r="H12" s="1">
-        <v>0.18771253526210785</v>
+        <v>0.18445482850074768</v>
       </c>
       <c r="I12" s="1">
-        <v>0.12451978772878647</v>
+        <v>0.1244753897190094</v>
       </c>
       <c r="J12" t="s">
         <v>2</v>
@@ -980,31 +1007,31 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F13" s="1">
-        <v>0.10353909520640105</v>
+        <v>0.10201331273817139</v>
       </c>
       <c r="G13" s="1">
-        <v>0.048582244664430618</v>
+        <v>0.047835890203714371</v>
       </c>
       <c r="H13" s="1">
-        <v>0.035427875816822052</v>
+        <v>0.035268891602754593</v>
       </c>
       <c r="I13" s="1">
-        <v>0.12451978772878647</v>
+        <v>0.1244753897190094</v>
       </c>
       <c r="J13" t="s">
         <v>2</v>
@@ -1018,25 +1045,25 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.11198458105394465</v>
+        <v>-0.10589753346034296</v>
       </c>
       <c r="G14" s="1">
-        <v>0.087617971003055573</v>
+        <v>0.086773410439491272</v>
       </c>
       <c r="H14" s="1">
-        <v>0.20405921339988708</v>
+        <v>0.22502446174621582</v>
       </c>
       <c r="I14" s="1">
-        <v>0.32255089282989502</v>
+        <v>0.34093368053436279</v>
       </c>
       <c r="J14" t="s">
         <v>2</v>
@@ -1050,25 +1077,25 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F15" s="1">
-        <v>0.011971423480992833</v>
+        <v>0.02986298378221269</v>
       </c>
       <c r="G15" s="1">
-        <v>0.088852271437644958</v>
+        <v>0.087552882730960846</v>
       </c>
       <c r="H15" s="1">
-        <v>0.89308255910873413</v>
+        <v>0.73371469974517822</v>
       </c>
       <c r="I15" s="1">
-        <v>0.32255089282989502</v>
+        <v>0.34093368053436279</v>
       </c>
       <c r="J15" t="s">
         <v>2</v>
@@ -1082,25 +1109,25 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.0012110229376787792</v>
+        <v>-0.00077039913297744531</v>
       </c>
       <c r="G16" s="1">
-        <v>0.0017240274464711547</v>
+        <v>0.0016645675059407949</v>
       </c>
       <c r="H16" s="1">
-        <v>0.48397511243820191</v>
+        <v>0.6444404125213623</v>
       </c>
       <c r="I16" s="1">
-        <v>0.32255089282989502</v>
+        <v>0.34093368053436279</v>
       </c>
       <c r="J16" t="s">
         <v>2</v>
@@ -1114,25 +1141,25 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F17" s="1">
-        <v>0.14762573511127103</v>
+        <v>0.16538613082994566</v>
       </c>
       <c r="G17" s="1">
-        <v>0.054129373282194138</v>
+        <v>0.051539618521928787</v>
       </c>
       <c r="H17" s="1">
-        <v>0.0074970959685742855</v>
+        <v>0.0017629669746384025</v>
       </c>
       <c r="I17" s="1">
-        <v>0.32255089282989502</v>
+        <v>0.34093368053436279</v>
       </c>
       <c r="J17" t="s">
         <v>2</v>
@@ -1146,25 +1173,25 @@
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F18" s="1">
-        <v>0.22456434104853867</v>
+        <v>0.21401358251464159</v>
       </c>
       <c r="G18" s="1">
-        <v>0.096516236662864685</v>
+        <v>0.095604963600635529</v>
       </c>
       <c r="H18" s="1">
-        <v>0.021919790655374527</v>
+        <v>0.027277169749140739</v>
       </c>
       <c r="I18" s="1">
-        <v>0.32255089282989502</v>
+        <v>0.34093368053436279</v>
       </c>
       <c r="J18" t="s">
         <v>2</v>
@@ -1178,25 +1205,25 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F19" s="1">
-        <v>0.12880264874598973</v>
+        <v>0.12404105600795921</v>
       </c>
       <c r="G19" s="1">
-        <v>0.058024436235427856</v>
+        <v>0.057472299784421921</v>
       </c>
       <c r="H19" s="1">
-        <v>0.028603170067071915</v>
+        <v>0.033163279294967651</v>
       </c>
       <c r="I19" s="1">
-        <v>0.32255089282989502</v>
+        <v>0.34093368053436279</v>
       </c>
       <c r="J19" t="s">
         <v>2</v>
@@ -1204,31 +1231,31 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F20" s="1">
-        <v>0.046185151447203192</v>
+        <v>0.040530788126625104</v>
       </c>
       <c r="G20" s="1">
-        <v>0.032534632831811905</v>
+        <v>0.033845845609903336</v>
       </c>
       <c r="H20" s="1">
-        <v>0.15872375667095184</v>
+        <v>0.23377828299999237</v>
       </c>
       <c r="I20" s="1">
-        <v>0.1476048082113266</v>
+        <v>0.12964822351932526</v>
       </c>
       <c r="J20" t="s">
         <v>2</v>
@@ -1236,31 +1263,31 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.10100844317605231</v>
+        <v>-0.08810752241523942</v>
       </c>
       <c r="G21" s="1">
-        <v>0.065072625875473023</v>
+        <v>0.065727494657039642</v>
       </c>
       <c r="H21" s="1">
-        <v>0.12364230304956436</v>
+        <v>0.18294969201087952</v>
       </c>
       <c r="I21" s="1">
-        <v>0.1476048082113266</v>
+        <v>0.12964822351932526</v>
       </c>
       <c r="J21" t="s">
         <v>2</v>
@@ -1268,31 +1295,31 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.00037371459742473206</v>
+        <v>-0.00067262957036721852</v>
       </c>
       <c r="G22" s="1">
-        <v>0.0010103345848619938</v>
+        <v>0.001010921667329967</v>
       </c>
       <c r="H22" s="1">
-        <v>0.71221518516540527</v>
+        <v>0.50726372003555298</v>
       </c>
       <c r="I22" s="1">
-        <v>0.1476048082113266</v>
+        <v>0.12964822351932526</v>
       </c>
       <c r="J22" t="s">
         <v>2</v>
@@ -1300,31 +1327,31 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E23" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F23" s="1">
-        <v>0.0056089767350157894</v>
+        <v>0.012330063610919611</v>
       </c>
       <c r="G23" s="1">
-        <v>0.029924403876066208</v>
+        <v>0.030583562329411507</v>
       </c>
       <c r="H23" s="1">
-        <v>0.85168224573135376</v>
+        <v>0.68764269351959229</v>
       </c>
       <c r="I23" s="1">
-        <v>0.1476048082113266</v>
+        <v>0.12964822351932526</v>
       </c>
       <c r="J23" t="s">
         <v>2</v>
@@ -1332,31 +1359,31 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F24" s="1">
-        <v>0.077458952074366871</v>
+        <v>0.079894186909865869</v>
       </c>
       <c r="G24" s="1">
-        <v>0.054309077560901642</v>
+        <v>0.054887067526578903</v>
       </c>
       <c r="H24" s="1">
-        <v>0.15678782761096954</v>
+        <v>0.14845567941665649</v>
       </c>
       <c r="I24" s="1">
-        <v>0.1476048082113266</v>
+        <v>0.12964822351932526</v>
       </c>
       <c r="J24" t="s">
         <v>2</v>
@@ -1364,31 +1391,31 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E25" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F25" s="1">
-        <v>0.080693176747326331</v>
+        <v>0.073519228640783488</v>
       </c>
       <c r="G25" s="1">
-        <v>0.026704544201493263</v>
+        <v>0.026383768767118454</v>
       </c>
       <c r="H25" s="1">
-        <v>0.0031643363181501627</v>
+        <v>0.0063138222321867943</v>
       </c>
       <c r="I25" s="1">
-        <v>0.1476048082113266</v>
+        <v>0.12964822351932526</v>
       </c>
       <c r="J25" t="s">
         <v>2</v>
@@ -1396,31 +1423,31 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F26" s="1">
-        <v>0.060160809967814685</v>
+        <v>0.056933486871541386</v>
       </c>
       <c r="G26" s="1">
-        <v>0.045053265988826752</v>
+        <v>0.04572354257106781</v>
       </c>
       <c r="H26" s="1">
-        <v>0.18468491733074188</v>
+        <v>0.21581567823886871</v>
       </c>
       <c r="I26" s="1">
-        <v>0.15164534747600556</v>
+        <v>0.15153224766254425</v>
       </c>
       <c r="J26" t="s">
         <v>2</v>
@@ -1428,31 +1455,31 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.0723182789980302</v>
+        <v>-0.066125416666302922</v>
       </c>
       <c r="G27" s="1">
-        <v>0.07407774031162262</v>
+        <v>0.072455160319805145</v>
       </c>
       <c r="H27" s="1">
-        <v>0.33120673894882202</v>
+        <v>0.36350336670875549</v>
       </c>
       <c r="I27" s="1">
-        <v>0.15164534747600556</v>
+        <v>0.15153224766254425</v>
       </c>
       <c r="J27" t="s">
         <v>2</v>
@@ -1460,31 +1487,31 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.0013043179283806659</v>
+        <v>-0.0014782052025612892</v>
       </c>
       <c r="G28" s="1">
-        <v>0.0011875545606017113</v>
+        <v>0.0011979403207078576</v>
       </c>
       <c r="H28" s="1">
-        <v>0.27459993958473206</v>
+        <v>0.21994833648204803</v>
       </c>
       <c r="I28" s="1">
-        <v>0.15164534747600556</v>
+        <v>0.15153224766254425</v>
       </c>
       <c r="J28" t="s">
         <v>2</v>
@@ -1492,31 +1519,31 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E29" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F29" s="1">
-        <v>0.0043303595839324395</v>
+        <v>0.015952630513066956</v>
       </c>
       <c r="G29" s="1">
-        <v>0.032482821494340897</v>
+        <v>0.033431831747293472</v>
       </c>
       <c r="H29" s="1">
-        <v>0.89420402050018311</v>
+        <v>0.63422417640686035</v>
       </c>
       <c r="I29" s="1">
-        <v>0.15164534747600556</v>
+        <v>0.15153224766254425</v>
       </c>
       <c r="J29" t="s">
         <v>2</v>
@@ -1524,31 +1551,31 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F30" s="1">
-        <v>0.14228638593331908</v>
+        <v>0.13944308878643347</v>
       </c>
       <c r="G30" s="1">
-        <v>0.05247555673122406</v>
+        <v>0.05207381397485733</v>
       </c>
       <c r="H30" s="1">
-        <v>0.0078385109081864357</v>
+        <v>0.0085907019674777985</v>
       </c>
       <c r="I30" s="1">
-        <v>0.15164534747600556</v>
+        <v>0.15153224766254425</v>
       </c>
       <c r="J30" t="s">
         <v>2</v>
@@ -1556,31 +1583,31 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E31" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F31" s="1">
-        <v>0.016131242348303536</v>
+        <v>0.010690827812753901</v>
       </c>
       <c r="G31" s="1">
-        <v>0.033707734197378159</v>
+        <v>0.033412139862775803</v>
       </c>
       <c r="H31" s="1">
-        <v>0.6332547664642334</v>
+        <v>0.74962210655212402</v>
       </c>
       <c r="I31" s="1">
-        <v>0.15164534747600556</v>
+        <v>0.15153224766254425</v>
       </c>
       <c r="J31" t="s">
         <v>2</v>
@@ -1594,25 +1621,25 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.021423734413939612</v>
+        <v>-0.026713542467637189</v>
       </c>
       <c r="G32" s="1">
-        <v>0.072123542428016663</v>
+        <v>0.072486169636249542</v>
       </c>
       <c r="H32" s="1">
-        <v>0.76702678203582764</v>
+        <v>0.71321088075637817</v>
       </c>
       <c r="I32" s="1">
-        <v>0.093699194490909577</v>
+        <v>0.086727350950241089</v>
       </c>
       <c r="J32" t="s">
         <v>2</v>
@@ -1626,25 +1653,25 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E33" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F33" s="1">
-        <v>0.062157094346826716</v>
+        <v>0.042465403427239916</v>
       </c>
       <c r="G33" s="1">
-        <v>0.092962600290775299</v>
+        <v>0.092538230121135712</v>
       </c>
       <c r="H33" s="1">
-        <v>0.50521630048751831</v>
+        <v>0.64724862575531006</v>
       </c>
       <c r="I33" s="1">
-        <v>0.093699194490909577</v>
+        <v>0.086727350950241089</v>
       </c>
       <c r="J33" t="s">
         <v>2</v>
@@ -1658,25 +1685,25 @@
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E34" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.0022277766427665196</v>
+        <v>-0.0025734277448592972</v>
       </c>
       <c r="G34" s="1">
-        <v>0.0018740278901532292</v>
+        <v>0.0018946169875562191</v>
       </c>
       <c r="H34" s="1">
-        <v>0.23723992705345154</v>
+        <v>0.17725750803947449</v>
       </c>
       <c r="I34" s="1">
-        <v>0.093699194490909577</v>
+        <v>0.086727350950241089</v>
       </c>
       <c r="J34" t="s">
         <v>2</v>
@@ -1690,25 +1717,25 @@
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E35" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F35" s="1">
-        <v>0.11343977186994238</v>
+        <v>0.11276201251737389</v>
       </c>
       <c r="G35" s="1">
-        <v>0.052177552133798599</v>
+        <v>0.053173869848251343</v>
       </c>
       <c r="H35" s="1">
-        <v>0.031964454799890518</v>
+        <v>0.036285612732172012</v>
       </c>
       <c r="I35" s="1">
-        <v>0.093699194490909577</v>
+        <v>0.086727350950241089</v>
       </c>
       <c r="J35" t="s">
         <v>2</v>
@@ -1722,25 +1749,25 @@
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E36" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.09794953415849203</v>
+        <v>-0.097190615111588649</v>
       </c>
       <c r="G36" s="1">
-        <v>0.081267513334751129</v>
+        <v>0.082339182496070862</v>
       </c>
       <c r="H36" s="1">
-        <v>0.23083324730396271</v>
+        <v>0.24049551784992218</v>
       </c>
       <c r="I36" s="1">
-        <v>0.093699194490909577</v>
+        <v>0.086727350950241089</v>
       </c>
       <c r="J36" t="s">
         <v>2</v>
@@ -1754,25 +1781,25 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E37" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F37" s="1">
-        <v>0.02626284988924783</v>
+        <v>0.028163978779372604</v>
       </c>
       <c r="G37" s="1">
-        <v>0.054750833660364151</v>
+        <v>0.05497942864894867</v>
       </c>
       <c r="H37" s="1">
-        <v>0.63246256113052368</v>
+        <v>0.60953199863433838</v>
       </c>
       <c r="I37" s="1">
-        <v>0.093699194490909577</v>
+        <v>0.086727350950241089</v>
       </c>
       <c r="J37" t="s">
         <v>2</v>
@@ -1780,31 +1807,31 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E38" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.027246431329447953</v>
+        <v>-0.02959703266752076</v>
       </c>
       <c r="G38" s="1">
-        <v>0.033856101334095001</v>
+        <v>0.034145649522542953</v>
       </c>
       <c r="H38" s="1">
-        <v>0.42278739809989929</v>
+        <v>0.38801613450050354</v>
       </c>
       <c r="I38" s="1">
-        <v>0.071979537606239319</v>
+        <v>0.075183078646659851</v>
       </c>
       <c r="J38" t="s">
         <v>2</v>
@@ -1812,31 +1839,31 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.065025791041110045</v>
+        <v>-0.060057105853714078</v>
       </c>
       <c r="G39" s="1">
-        <v>0.059578143060207367</v>
+        <v>0.057804763317108154</v>
       </c>
       <c r="H39" s="1">
-        <v>0.27760270237922669</v>
+        <v>0.30118530988693237</v>
       </c>
       <c r="I39" s="1">
-        <v>0.071979537606239319</v>
+        <v>0.075183078646659851</v>
       </c>
       <c r="J39" t="s">
         <v>2</v>
@@ -1844,31 +1871,31 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E40" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.0013324526381361817</v>
+        <v>-0.0014522897221231326</v>
       </c>
       <c r="G40" s="1">
-        <v>0.0011830227449536324</v>
+        <v>0.0011787067633122206</v>
       </c>
       <c r="H40" s="1">
-        <v>0.26262578368186951</v>
+        <v>0.22063623368740082</v>
       </c>
       <c r="I40" s="1">
-        <v>0.071979537606239319</v>
+        <v>0.075183078646659851</v>
       </c>
       <c r="J40" t="s">
         <v>2</v>
@@ -1876,31 +1903,31 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E41" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.013341753183540623</v>
+        <v>-0.00779210921156317</v>
       </c>
       <c r="G41" s="1">
-        <v>0.026849959045648575</v>
+        <v>0.0273545291274786</v>
       </c>
       <c r="H41" s="1">
-        <v>0.62030810117721558</v>
+        <v>0.7763100266456604</v>
       </c>
       <c r="I41" s="1">
-        <v>0.071979537606239319</v>
+        <v>0.075183078646659851</v>
       </c>
       <c r="J41" t="s">
         <v>2</v>
@@ -1908,31 +1935,31 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F42" s="1">
-        <v>0.023671119165391885</v>
+        <v>0.02317967521792378</v>
       </c>
       <c r="G42" s="1">
-        <v>0.033756788820028305</v>
+        <v>0.033492203801870346</v>
       </c>
       <c r="H42" s="1">
-        <v>0.48472842574119568</v>
+        <v>0.4903930127620697</v>
       </c>
       <c r="I42" s="1">
-        <v>0.071979537606239319</v>
+        <v>0.075183078646659851</v>
       </c>
       <c r="J42" t="s">
         <v>2</v>
@@ -1940,31 +1967,31 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E43" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F43" s="1">
-        <v>0.034058170335340358</v>
+        <v>0.030580975719080573</v>
       </c>
       <c r="G43" s="1">
-        <v>0.0288377795368433</v>
+        <v>0.02839849516749382</v>
       </c>
       <c r="H43" s="1">
-        <v>0.2402862012386322</v>
+        <v>0.28399112820625305</v>
       </c>
       <c r="I43" s="1">
-        <v>0.071979537606239319</v>
+        <v>0.075183078646659851</v>
       </c>
       <c r="J43" t="s">
         <v>2</v>
